--- a/knowledge_source/Windchill GPDM & Windchill NA/Windchill GPDM/GPDM-User Management/EMEA, LA & AP Training Matrix.xlsx
+++ b/knowledge_source/Windchill GPDM & Windchill NA/Windchill GPDM/GPDM-User Management/EMEA, LA & AP Training Matrix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2469233_cognizant_com/Documents/Documents/Stand Up - Global Support Meeting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="562" documentId="13_ncr:1_{459239DA-DEA4-4DFE-A496-D3DDCF2F9A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C398321-8E48-4459-9308-E6A5FE952DB0}"/>
+  <xr:revisionPtr revIDLastSave="599" documentId="13_ncr:1_{459239DA-DEA4-4DFE-A496-D3DDCF2F9A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C8292A8-1507-4E72-AC46-6794F93018CD}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="2" xr2:uid="{676C3396-962B-4473-8949-DD3B4DF71E8D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="4" xr2:uid="{676C3396-962B-4473-8949-DD3B4DF71E8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Bluspace Link" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Groups" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Roles-Capability&amp;Tranings'!$A$1:$E$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Roles-Capability&amp;Tranings'!$A$1:$D$61</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="465">
   <si>
     <t>https://bluespace.fmeone.com/pages/viewpage.action?pageId=283768310&amp;spaceKey=GlobalPDM&amp;title=EMEA%2BLA%2BAP%2BTraining%2BMatrix#EMEA,LA&amp;APTrainingMatrix-WindchillLearningPathEMEA,LA&amp;AP</t>
   </si>
@@ -61,6 +61,9 @@
     <t>Required Training</t>
   </si>
   <si>
+    <t>Self directed trainings</t>
+  </si>
+  <si>
     <t>Digital Twin</t>
   </si>
   <si>
@@ -355,10 +358,16 @@
     <t>1. Verification Baseline</t>
   </si>
   <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>Verification Baseline Approver</t>
   </si>
   <si>
     <t>Approves verification baselines during Verification and Validation</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
   <si>
     <t>Unique Device Identification</t>
@@ -1379,13 +1388,23 @@
     <t>verification implementation manager</t>
   </si>
   <si>
-    <t>Verification Management (Self Study)</t>
+    <t>(Self Study) (https://bluespace.fmeone.com/spaces/GlobalPDM/pages/75704839/Quick+Reference+Guides#
+QuickReferenceGuides-LinkingVerificationDocumentstoPartsLinkingVerificationDocumentstoParts)</t>
   </si>
   <si>
     <t>Verification Management</t>
   </si>
   <si>
     <t>Establishes the link between Parts and verification documentation</t>
+  </si>
+  <si>
+    <t>For this role  we need to get confirmation from CAs, Pre-requiste for this role they should have undergone Pdoc training.</t>
+  </si>
+  <si>
+    <t>FMEA Document Manager</t>
+  </si>
+  <si>
+    <t>Self Study(https://bluespace.fmeone.com/spaces/GlobalPDM/pages/75704839/Quick+Reference+Guides#QuickReferenceGuides-LinkingFMEADocuments)</t>
   </si>
   <si>
     <t>Groups</t>
@@ -1613,7 +1632,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1656,8 +1675,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1793,12 +1818,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1822,12 +1873,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1839,15 +1884,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1886,9 +1922,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1911,7 +1944,38 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1921,7 +1985,10 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1944,6 +2011,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2295,17 +2368,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F51A01E5-D8A9-43E5-880B-AF9082248A63}">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultColWidth="12.140625" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="15.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="12.140625" style="6"/>
+    <col min="4" max="4" width="33" style="6" customWidth="1"/>
+    <col min="5" max="5" width="19" style="6" customWidth="1"/>
+    <col min="6" max="16384" width="12.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5" ht="15">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -2315,723 +2389,798 @@
       <c r="C1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="38" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="43" t="s">
+      <c r="E1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="44" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="50" t="s">
         <v>6</v>
       </c>
+      <c r="B2" s="51" t="s">
+        <v>7</v>
+      </c>
       <c r="C2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="46" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="43"/>
-      <c r="B3" s="44"/>
+      <c r="D2" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="44"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="50"/>
+      <c r="B3" s="51"/>
       <c r="C3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="54"/>
+      <c r="E3" s="37"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="37"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="50"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="53"/>
+      <c r="E5" s="37"/>
+    </row>
+    <row r="6" spans="1:5" ht="26.1">
+      <c r="A6" s="50"/>
+      <c r="B6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="37"/>
+    </row>
+    <row r="7" spans="1:5" ht="65.099999999999994">
+      <c r="A7" s="50"/>
+      <c r="B7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="52"/>
+      <c r="D7" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="37"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="50"/>
+      <c r="B8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="52"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="37"/>
+    </row>
+    <row r="9" spans="1:5" ht="26.1">
+      <c r="A9" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="37"/>
+    </row>
+    <row r="10" spans="1:5" ht="39">
+      <c r="A10" s="50"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="37"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="37"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="50"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="53"/>
+      <c r="E12" s="37"/>
+    </row>
+    <row r="13" spans="1:5" ht="39">
+      <c r="A13" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="37"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="50"/>
+      <c r="B14" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="37"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="50"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="53"/>
+      <c r="E15" s="37"/>
+    </row>
+    <row r="16" spans="1:5" ht="26.1">
+      <c r="A16" s="50"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="53"/>
+      <c r="E16" s="37"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="50"/>
+      <c r="B17" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="37"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="50"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="53"/>
+      <c r="E18" s="37"/>
+    </row>
+    <row r="19" spans="1:5" ht="26.1">
+      <c r="A19" s="50"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="53"/>
+      <c r="E19" s="37"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="50"/>
+      <c r="B20" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="37"/>
+    </row>
+    <row r="21" spans="1:5" ht="26.1">
+      <c r="A21" s="50"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="53"/>
+      <c r="E21" s="37"/>
+    </row>
+    <row r="22" spans="1:5" ht="26.1">
+      <c r="A22" s="50"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="53"/>
+      <c r="E22" s="37"/>
+    </row>
+    <row r="23" spans="1:5" ht="39">
+      <c r="A23" s="50"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="53"/>
+      <c r="E23" s="37"/>
+    </row>
+    <row r="24" spans="1:5" ht="26.1">
+      <c r="A24" s="50"/>
+      <c r="B24" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="37"/>
+    </row>
+    <row r="25" spans="1:5" ht="26.1">
+      <c r="A25" s="50"/>
+      <c r="B25" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="53"/>
+      <c r="E25" s="37"/>
+    </row>
+    <row r="26" spans="1:5" ht="26.1">
+      <c r="A26" s="50"/>
+      <c r="B26" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="53"/>
+      <c r="E26" s="37"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="50"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="53"/>
+      <c r="E27" s="37"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="50"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="53"/>
+      <c r="E28" s="37"/>
+    </row>
+    <row r="29" spans="1:5" ht="26.1">
+      <c r="A29" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="37"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="50"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="53"/>
+      <c r="E30" s="37"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="50"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="53"/>
+      <c r="E31" s="37"/>
+    </row>
+    <row r="32" spans="1:5" ht="26.1">
+      <c r="A32" s="50"/>
+      <c r="B32" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="53"/>
+      <c r="E32" s="37"/>
+    </row>
+    <row r="33" spans="1:5" ht="51.95">
+      <c r="A33" s="50"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="53"/>
+      <c r="E33" s="37"/>
+    </row>
+    <row r="34" spans="1:5" ht="51.95">
+      <c r="A34" s="50"/>
+      <c r="B34" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="E34" s="37"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="50"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="42"/>
+      <c r="E35" s="37"/>
+    </row>
+    <row r="36" spans="1:5" ht="78">
+      <c r="A36" s="50"/>
+      <c r="B36" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" s="37"/>
+    </row>
+    <row r="37" spans="1:5" ht="51.95">
+      <c r="A37" s="50"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="42"/>
+      <c r="E37" s="37"/>
+    </row>
+    <row r="38" spans="1:5" ht="51.95">
+      <c r="A38" s="50"/>
+      <c r="B38" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" s="37"/>
+    </row>
+    <row r="39" spans="1:5" ht="26.1">
+      <c r="A39" s="50"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D39" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="37"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="50"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="42"/>
+      <c r="E40" s="37"/>
+    </row>
+    <row r="41" spans="1:5" ht="65.099999999999994">
+      <c r="A41" s="50"/>
+      <c r="B41" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="37"/>
+    </row>
+    <row r="42" spans="1:5" ht="39">
+      <c r="A42" s="50"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42" s="42"/>
+      <c r="E42" s="37"/>
+    </row>
+    <row r="43" spans="1:5" ht="51.95">
+      <c r="A43" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="E43" s="37"/>
+    </row>
+    <row r="44" spans="1:5" ht="26.1">
+      <c r="A44" s="50"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D44" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" s="37"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="50"/>
+      <c r="B45" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="E45" s="37"/>
+    </row>
+    <row r="46" spans="1:5" ht="26.1">
+      <c r="A46" s="50"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D46" s="54"/>
+      <c r="E46" s="37"/>
+    </row>
+    <row r="47" spans="1:5" ht="39">
+      <c r="A47" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D47" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="37"/>
+    </row>
+    <row r="48" spans="1:5" ht="39">
+      <c r="A48" s="50"/>
+      <c r="B48" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="E48" s="37"/>
+    </row>
+    <row r="49" spans="1:5" ht="26.1">
+      <c r="A49" s="50"/>
+      <c r="B49" s="51"/>
+      <c r="C49" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D49" s="42"/>
+      <c r="E49" s="37"/>
+    </row>
+    <row r="50" spans="1:5" ht="26.1">
+      <c r="A50" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E50" s="37" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="39">
+      <c r="A51" s="50"/>
+      <c r="B51" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D51" s="53"/>
+      <c r="E51" s="37" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="26.1">
+      <c r="A52" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="E52" s="37"/>
+    </row>
+    <row r="53" spans="1:5" ht="26.1">
+      <c r="A53" s="50"/>
+      <c r="B53" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D53" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="46"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="45" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="43"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="8" t="s">
+      <c r="E53" s="37"/>
+    </row>
+    <row r="54" spans="1:5" ht="26.1">
+      <c r="A54" s="50"/>
+      <c r="B54" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D54" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="E54" s="37"/>
+    </row>
+    <row r="55" spans="1:5" ht="26.1">
+      <c r="A55" s="50"/>
+      <c r="B55" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D55" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="37"/>
+    </row>
+    <row r="56" spans="1:5" ht="26.1">
+      <c r="A56" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56" s="37"/>
+    </row>
+    <row r="57" spans="1:5" ht="26.1">
+      <c r="A57" s="50"/>
+      <c r="B57" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D57" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E57" s="37"/>
+    </row>
+    <row r="58" spans="1:5" ht="26.1">
+      <c r="A58" s="50"/>
+      <c r="B58" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="52" t="s">
+        <v>125</v>
+      </c>
+      <c r="D58" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E58" s="37"/>
+    </row>
+    <row r="59" spans="1:5" ht="90.95">
+      <c r="A59" s="50"/>
+      <c r="B59" s="51"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="E59" s="37"/>
+    </row>
+    <row r="60" spans="1:5" ht="26.1">
+      <c r="A60" s="50"/>
+      <c r="B60" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D60" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E60" s="37"/>
+    </row>
+    <row r="61" spans="1:5" ht="26.1">
+      <c r="A61" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="B61" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="D61" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="E61" s="37"/>
+    </row>
+    <row r="62" spans="1:5" ht="39">
+      <c r="A62" s="50"/>
+      <c r="B62" s="51"/>
+      <c r="C62" s="52"/>
+      <c r="D62" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="E62" s="37"/>
+    </row>
+    <row r="63" spans="1:5" ht="26.1">
+      <c r="A63" s="50"/>
+      <c r="B63" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D63" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="45"/>
-    </row>
-    <row r="6" spans="1:4" ht="26.1">
-      <c r="A6" s="43"/>
-      <c r="B6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="65.099999999999994">
-      <c r="A7" s="43"/>
-      <c r="B7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="43"/>
-      <c r="B8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="12"/>
-    </row>
-    <row r="9" spans="1:4" ht="26.1">
-      <c r="A9" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="39">
-      <c r="A10" s="43"/>
-      <c r="B10" s="44"/>
-      <c r="C10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="45" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="45"/>
-    </row>
-    <row r="13" spans="1:4" ht="39">
-      <c r="A13" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="45" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="45"/>
-    </row>
-    <row r="16" spans="1:4" ht="26.1">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="45"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="43"/>
-      <c r="B17" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="45" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="43"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="45"/>
-    </row>
-    <row r="19" spans="1:4" ht="26.1">
-      <c r="A19" s="43"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="45"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="43"/>
-      <c r="B20" s="44" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="45" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="26.1">
-      <c r="A21" s="43"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="45"/>
-    </row>
-    <row r="22" spans="1:4" ht="26.1">
-      <c r="A22" s="43"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="45"/>
-    </row>
-    <row r="23" spans="1:4" ht="39">
-      <c r="A23" s="43"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="45"/>
-    </row>
-    <row r="24" spans="1:4" ht="26.1">
-      <c r="A24" s="43"/>
-      <c r="B24" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="45" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="26.1">
-      <c r="A25" s="43"/>
-      <c r="B25" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="45"/>
-    </row>
-    <row r="26" spans="1:4" ht="26.1">
-      <c r="A26" s="43"/>
-      <c r="B26" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="45"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="43"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="45"/>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="43"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="45"/>
-    </row>
-    <row r="29" spans="1:4" ht="26.1">
-      <c r="A29" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="45" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="43"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="45"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="43"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" s="45"/>
-    </row>
-    <row r="32" spans="1:4" ht="26.1">
-      <c r="A32" s="43"/>
-      <c r="B32" s="44" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="45"/>
-    </row>
-    <row r="33" spans="1:4" ht="51.95">
-      <c r="A33" s="43"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="45"/>
-    </row>
-    <row r="34" spans="1:4" ht="51.95">
-      <c r="A34" s="43"/>
-      <c r="B34" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="43"/>
-      <c r="B35" s="44"/>
-      <c r="C35" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="12"/>
-    </row>
-    <row r="36" spans="1:4" ht="78">
-      <c r="A36" s="43"/>
-      <c r="B36" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="51.95">
-      <c r="A37" s="43"/>
-      <c r="B37" s="44"/>
-      <c r="C37" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="12"/>
-    </row>
-    <row r="38" spans="1:4" ht="51.95">
-      <c r="A38" s="43"/>
-      <c r="B38" s="44" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="26.1">
-      <c r="A39" s="43"/>
-      <c r="B39" s="44"/>
-      <c r="C39" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="43"/>
-      <c r="B40" s="44"/>
-      <c r="C40" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" s="12"/>
-    </row>
-    <row r="41" spans="1:4" ht="65.099999999999994">
-      <c r="A41" s="43"/>
-      <c r="B41" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="39">
-      <c r="A42" s="43"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D42" s="12"/>
-    </row>
-    <row r="43" spans="1:4" ht="51.95">
-      <c r="A43" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="26.1">
-      <c r="A44" s="43"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="43"/>
-      <c r="B45" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D45" s="46" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="26.1">
-      <c r="A46" s="43"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" s="46"/>
-    </row>
-    <row r="47" spans="1:4" ht="39">
-      <c r="A47" s="43" t="s">
-        <v>92</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="39">
-      <c r="A48" s="43"/>
-      <c r="B48" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="26.1">
-      <c r="A49" s="43"/>
-      <c r="B49" s="44"/>
-      <c r="C49" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" s="12"/>
-    </row>
-    <row r="50" spans="1:4" ht="26.1">
-      <c r="A50" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D50" s="45" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="39">
-      <c r="A51" s="43"/>
-      <c r="B51" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" s="45"/>
-    </row>
-    <row r="52" spans="1:4" ht="26.1">
-      <c r="A52" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="26.1">
-      <c r="A53" s="43"/>
-      <c r="B53" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="26.1">
-      <c r="A54" s="43"/>
-      <c r="B54" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="26.1">
-      <c r="A55" s="43"/>
-      <c r="B55" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="26.1">
-      <c r="A56" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="26.1">
-      <c r="A57" s="43"/>
-      <c r="B57" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="26.1">
-      <c r="A58" s="43"/>
-      <c r="B58" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="C58" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="90.95">
-      <c r="A59" s="43"/>
-      <c r="B59" s="44"/>
-      <c r="C59" s="45"/>
-      <c r="D59" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="26.1">
-      <c r="A60" s="43"/>
-      <c r="B60" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="26.1">
-      <c r="A61" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="B61" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="C61" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="39">
-      <c r="A62" s="43"/>
-      <c r="B62" s="44"/>
-      <c r="C62" s="45"/>
-      <c r="D62" s="9" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="26.1">
-      <c r="A63" s="43"/>
-      <c r="B63" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="26.1">
-      <c r="A64" s="43"/>
-      <c r="B64" s="44"/>
+      <c r="E63" s="37"/>
+    </row>
+    <row r="64" spans="1:5" ht="26.1">
+      <c r="A64" s="50"/>
+      <c r="B64" s="51"/>
       <c r="C64" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="39">
-      <c r="A65" s="43"/>
-      <c r="B65" s="44"/>
+        <v>136</v>
+      </c>
+      <c r="D64" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="E64" s="37"/>
+    </row>
+    <row r="65" spans="1:5" ht="39">
+      <c r="A65" s="50"/>
+      <c r="B65" s="51"/>
       <c r="C65" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="43"/>
-      <c r="B66" s="44"/>
+        <v>138</v>
+      </c>
+      <c r="D65" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="E65" s="37"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="50"/>
+      <c r="B66" s="51"/>
       <c r="C66" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D66" s="42"/>
+      <c r="E66" s="37"/>
+    </row>
+    <row r="67" spans="1:5" ht="39">
+      <c r="A67" s="50"/>
+      <c r="B67" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D67" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="37"/>
+    </row>
+    <row r="68" spans="1:5" ht="26.1">
+      <c r="A68" s="50"/>
+      <c r="B68" s="51"/>
+      <c r="C68" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D68" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="D66" s="12"/>
-    </row>
-    <row r="67" spans="1:4" ht="39">
-      <c r="A67" s="43"/>
-      <c r="B67" s="44" t="s">
-        <v>138</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="26.1">
-      <c r="A68" s="43"/>
-      <c r="B68" s="44"/>
-      <c r="C68" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="39">
-      <c r="A69" s="43"/>
-      <c r="B69" s="44"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="8" t="s">
-        <v>141</v>
-      </c>
+      <c r="E68" s="43"/>
+    </row>
+    <row r="69" spans="1:5" ht="39">
+      <c r="A69" s="50"/>
+      <c r="B69" s="51"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="E69" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -3101,512 +3250,512 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.5">
-      <c r="A1" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>144</v>
+      <c r="A1" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30.75">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30.75">
+      <c r="A3" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="76.5">
+      <c r="A4" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="45.75">
+      <c r="A6" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="43.5">
+      <c r="A7" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="29.25">
+      <c r="A9" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="43.5">
+      <c r="A10" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="72.75">
+      <c r="A11" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="43.5">
+      <c r="A12" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="29.25">
+      <c r="A13" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="43.5">
+      <c r="A14" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="43.5">
+      <c r="A15" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="57.75">
+      <c r="A16" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="45.75">
+      <c r="A17" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="60.75">
+      <c r="A18" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="45.75">
+      <c r="A19" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="43.5">
+      <c r="A20" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="91.5">
+      <c r="A21" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="57.75">
+      <c r="A22" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="29.25">
+      <c r="A23" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="91.5">
+      <c r="A24" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="76.5">
+      <c r="A25" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="60.75">
+      <c r="A28" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="43.5">
+      <c r="A29" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="29.25">
+      <c r="A30" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="72.75">
+      <c r="A33" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="60.75">
+      <c r="A34" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="45.75">
+      <c r="A35" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="45.75">
+      <c r="A36" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="43.5">
+      <c r="A37" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15.75">
+      <c r="A38" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="B38" s="58"/>
+      <c r="C38" s="59"/>
+    </row>
+    <row r="39" spans="1:3" ht="16.5">
+      <c r="A39" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B39" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C39" s="22" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30.75">
-      <c r="A3" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="21" t="s">
+    <row r="40" spans="1:3" ht="43.5">
+      <c r="A40" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="29.25">
+      <c r="A41" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.75">
+      <c r="A42" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="B42" s="56"/>
+      <c r="C42" s="57"/>
+    </row>
+    <row r="43" spans="1:3" ht="16.5">
+      <c r="A43" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="22" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="76.5">
-      <c r="A4" s="21" t="s">
+    <row r="44" spans="1:3" ht="29.25">
+      <c r="A44" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="45.75">
-      <c r="A6" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="43.5">
-      <c r="A7" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="29.25">
-      <c r="A9" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="43.5">
-      <c r="A10" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="72.75">
-      <c r="A11" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="43.5">
-      <c r="A12" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="29.25">
-      <c r="A13" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="43.5">
-      <c r="A14" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="43.5">
-      <c r="A15" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="57.75">
-      <c r="A16" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="45.75">
-      <c r="A17" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="60.75">
-      <c r="A18" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="45.75">
-      <c r="A19" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="43.5">
-      <c r="A20" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="91.5">
-      <c r="A21" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="57.75">
-      <c r="A22" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="29.25">
-      <c r="A23" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="91.5">
-      <c r="A24" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="76.5">
-      <c r="A25" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="60.75">
-      <c r="A28" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="43.5">
-      <c r="A29" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="29.25">
-      <c r="A30" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="72.75">
-      <c r="A33" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="60.75">
-      <c r="A34" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="45.75">
-      <c r="A35" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="B35" s="22" t="s">
-        <v>214</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="45.75">
-      <c r="A36" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="43.5">
-      <c r="A37" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.75">
-      <c r="A38" s="47" t="s">
-        <v>219</v>
-      </c>
-      <c r="B38" s="50"/>
-      <c r="C38" s="51"/>
-    </row>
-    <row r="39" spans="1:3" ht="16.5">
-      <c r="A39" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="B39" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="43.5">
-      <c r="A40" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="B40" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="29.25">
-      <c r="A41" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="B41" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.75">
-      <c r="A42" s="47" t="s">
-        <v>224</v>
-      </c>
-      <c r="B42" s="48"/>
-      <c r="C42" s="49"/>
-    </row>
-    <row r="43" spans="1:3" ht="16.5">
-      <c r="A43" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="B43" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="C43" s="27" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="29.25">
-      <c r="A44" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="B44" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>147</v>
+      <c r="A45" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="B46" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="C46" s="21" t="s">
-        <v>147</v>
+      <c r="A46" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="43.5">
-      <c r="A47" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="B47" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="C47" s="21" t="s">
-        <v>147</v>
+      <c r="A47" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3630,229 +3779,229 @@
   <sheetData>
     <row r="1" spans="1:3" ht="14.45">
       <c r="A1" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.45">
-      <c r="A2" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="B2" s="53" t="s">
-        <v>235</v>
+      <c r="A2" s="60" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>238</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.45">
-      <c r="A3" s="52"/>
-      <c r="B3" s="53"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
       <c r="C3" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="26.1">
       <c r="A4" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.45">
       <c r="A5" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.45">
       <c r="A6" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.45">
       <c r="A7" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.45">
       <c r="A8" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="39">
       <c r="A9" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.45">
       <c r="A10" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14.45">
       <c r="A11" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="26.1">
       <c r="A12" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75">
-      <c r="A14" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="B14" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>254</v>
+      <c r="A14" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>186</v>
+      <c r="A15" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="38" t="s">
-        <v>257</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>186</v>
+      <c r="A16" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30.75">
-      <c r="A17" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="B17" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>260</v>
+      <c r="A17" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="38" t="s">
-        <v>261</v>
-      </c>
-      <c r="B18" s="38" t="s">
-        <v>262</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>186</v>
+      <c r="A18" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30.75">
-      <c r="A19" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="B19" s="38" t="s">
-        <v>264</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>186</v>
+      <c r="A19" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="38" t="s">
-        <v>265</v>
-      </c>
-      <c r="B20" s="38" t="s">
-        <v>266</v>
-      </c>
-      <c r="C20" s="39" t="s">
-        <v>186</v>
+      <c r="A20" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="B21" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>186</v>
+      <c r="A21" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="B22" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>186</v>
+      <c r="A22" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -3866,970 +4015,986 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57DB3D55-2C7D-4E44-BB5E-763AFC2F400D}">
-  <dimension ref="A1:I67"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:H67"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="75.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="139.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.140625" customWidth="1"/>
     <col min="4" max="4" width="141.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="62.140625" customWidth="1"/>
+    <col min="5" max="5" width="62.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15">
-      <c r="A1" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="B1" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="C1" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="D1" s="31" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="48" t="s">
         <v>272</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="B1" s="48" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15">
-      <c r="A2" s="30" t="s">
+      <c r="C1" s="48" t="s">
         <v>274</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="D1" s="48" t="s">
         <v>275</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="E1" s="49" t="s">
         <v>276</v>
       </c>
-      <c r="D2" s="30" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="F2" s="16"/>
-    </row>
-    <row r="3" spans="1:6" ht="29.25">
-      <c r="A3" s="30" t="s">
+      <c r="B2" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="C2" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="D2" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="E2" s="45"/>
+    </row>
+    <row r="3" spans="1:5" ht="29.25">
+      <c r="A3" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="F3" s="16"/>
-    </row>
-    <row r="4" spans="1:6" ht="15">
-      <c r="A4" s="30" t="s">
+      <c r="B3" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="C3" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="C4" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="D4" s="32" t="s">
+      <c r="D3" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="F4" s="16"/>
-    </row>
-    <row r="5" spans="1:6" ht="15">
-      <c r="A5" s="30" t="s">
+      <c r="E3" s="45"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B4" s="25" t="s">
         <v>286</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C4" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="D4" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="E4" s="45"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="25" t="s">
         <v>288</v>
       </c>
-      <c r="F5" s="16"/>
-    </row>
-    <row r="6" spans="1:6" ht="15">
-      <c r="A6" s="30" t="s">
+      <c r="B5" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="C5" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="D5" s="26" t="s">
         <v>291</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="E5" s="45"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="25" t="s">
         <v>292</v>
       </c>
-      <c r="F6" s="16"/>
-    </row>
-    <row r="7" spans="1:6" ht="15">
-      <c r="A7" s="30" t="s">
+      <c r="B6" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="C6" s="27" t="s">
         <v>294</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="D6" s="26" t="s">
         <v>295</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="E6" s="45"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="F7" s="16"/>
-    </row>
-    <row r="8" spans="1:6" ht="15">
-      <c r="A8" s="30" t="s">
+      <c r="B7" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="C7" s="27" t="s">
         <v>298</v>
       </c>
-      <c r="C8" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="D8" s="32" t="s">
+      <c r="D7" s="26" t="s">
         <v>299</v>
       </c>
-      <c r="F8" s="16"/>
-    </row>
-    <row r="9" spans="1:6" ht="15">
-      <c r="A9" s="30" t="s">
-        <v>257</v>
-      </c>
-      <c r="B9" s="30" t="s">
+      <c r="E7" s="45"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="E8" s="45"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>303</v>
+      </c>
+      <c r="E9" s="45"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="E10" s="45"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="E11" s="45"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="E12" s="45"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="E13" s="45"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="E14" s="45"/>
+    </row>
+    <row r="15" spans="1:5" ht="29.25">
+      <c r="A15" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="29.25">
+      <c r="A16" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="E16" s="45"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="E17" s="45"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="E18" s="45"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="45"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="25" t="s">
+        <v>336</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="E20" s="45"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="E21" s="45"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>340</v>
+      </c>
+      <c r="E22" s="45"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E23" s="45"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="25" t="s">
+        <v>342</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>344</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>345</v>
+      </c>
+      <c r="E24" s="45"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="25" t="s">
+        <v>346</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>344</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>347</v>
+      </c>
+      <c r="E25" s="45"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="25" t="s">
+        <v>348</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>349</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="E26" s="45"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="E27" s="45"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" s="45"/>
+    </row>
+    <row r="29" spans="1:5" ht="29.25">
+      <c r="A29" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="E29" s="45"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="E30" s="45"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="25" t="s">
+        <v>361</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>362</v>
+      </c>
+      <c r="E31" s="45"/>
+    </row>
+    <row r="32" spans="1:5" ht="29.25">
+      <c r="A32" s="25" t="s">
+        <v>363</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>366</v>
+      </c>
+      <c r="E32" s="45"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="E33" s="45"/>
+    </row>
+    <row r="34" spans="1:5" ht="43.5">
+      <c r="A34" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>370</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>371</v>
+      </c>
+      <c r="E34" s="46" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="C35" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>375</v>
+      </c>
+      <c r="E35" s="45"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="E36" s="45"/>
+    </row>
+    <row r="37" spans="1:5" ht="29.25">
+      <c r="A37" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="E37" s="45"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="25" t="s">
+        <v>381</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="E38" s="45"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="C39" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>383</v>
+      </c>
+      <c r="E39" s="45"/>
+    </row>
+    <row r="40" spans="1:5" ht="29.25">
+      <c r="A40" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="E40" s="45"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25" t="s">
+        <v>388</v>
+      </c>
+      <c r="E41" s="45"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="C42" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>276</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>300</v>
-      </c>
-      <c r="F9" s="16"/>
-    </row>
-    <row r="10" spans="1:6" ht="15">
-      <c r="A10" s="30" t="s">
-        <v>301</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>304</v>
-      </c>
-      <c r="F10" s="16"/>
-    </row>
-    <row r="11" spans="1:6" ht="15">
-      <c r="A11" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>306</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>308</v>
-      </c>
-      <c r="F11" s="16"/>
-    </row>
-    <row r="12" spans="1:6" ht="15">
-      <c r="A12" s="30" t="s">
-        <v>309</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>311</v>
-      </c>
-      <c r="F12" s="16"/>
-    </row>
-    <row r="13" spans="1:6" ht="15">
-      <c r="A13" s="30" t="s">
-        <v>312</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>313</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>314</v>
-      </c>
-      <c r="F13" s="16"/>
-    </row>
-    <row r="14" spans="1:6" ht="15">
-      <c r="A14" s="30" t="s">
-        <v>315</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>316</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="D14" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="F14" s="16"/>
-    </row>
-    <row r="15" spans="1:6" ht="29.25">
-      <c r="A15" s="30" t="s">
-        <v>318</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>319</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>320</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="29.25">
-      <c r="A16" s="30" t="s">
-        <v>322</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>323</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>324</v>
-      </c>
-      <c r="F16" s="16"/>
-    </row>
-    <row r="17" spans="1:6" ht="15">
-      <c r="A17" s="30" t="s">
-        <v>325</v>
-      </c>
-      <c r="B17" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>240</v>
-      </c>
-      <c r="F17" s="16"/>
-    </row>
-    <row r="18" spans="1:6" ht="15">
-      <c r="A18" s="30" t="s">
-        <v>327</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>329</v>
-      </c>
-      <c r="F18" s="16"/>
-    </row>
-    <row r="19" spans="1:6" ht="15">
-      <c r="A19" s="30" t="s">
-        <v>330</v>
-      </c>
-      <c r="B19" s="30" t="s">
-        <v>331</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="F19" s="16"/>
-    </row>
-    <row r="20" spans="1:6" ht="15">
-      <c r="A20" s="30" t="s">
-        <v>333</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>331</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>334</v>
-      </c>
-      <c r="F20" s="16"/>
-    </row>
-    <row r="21" spans="1:6" ht="15">
-      <c r="A21" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="B21" s="30" t="s">
-        <v>283</v>
-      </c>
-      <c r="C21" s="33" t="s">
-        <v>276</v>
-      </c>
-      <c r="D21" s="30" t="s">
+      <c r="D42" s="25" t="s">
+        <v>391</v>
+      </c>
+      <c r="E42" s="45"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="C43" s="26" t="s">
         <v>335</v>
       </c>
-      <c r="F21" s="16"/>
-    </row>
-    <row r="22" spans="1:6" ht="15">
-      <c r="A22" s="30" t="s">
-        <v>336</v>
-      </c>
-      <c r="B22" s="30" t="s">
-        <v>283</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>276</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>337</v>
-      </c>
-      <c r="F22" s="16"/>
-    </row>
-    <row r="23" spans="1:6" ht="15">
-      <c r="A23" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="F23" s="16"/>
-    </row>
-    <row r="24" spans="1:6" ht="15">
-      <c r="A24" s="30" t="s">
-        <v>339</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>340</v>
-      </c>
-      <c r="C24" s="30" t="s">
+      <c r="D43" s="26" t="s">
+        <v>394</v>
+      </c>
+      <c r="E43" s="45"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="25" t="s">
+        <v>395</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>396</v>
+      </c>
+      <c r="E44" s="45"/>
+    </row>
+    <row r="45" spans="1:5" ht="43.5">
+      <c r="A45" s="25" t="s">
+        <v>397</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="E45" s="45"/>
+    </row>
+    <row r="46" spans="1:5" ht="29.25">
+      <c r="A46" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="B46" s="25" t="s">
         <v>341</v>
       </c>
-      <c r="D24" s="30" t="s">
-        <v>342</v>
-      </c>
-      <c r="F24" s="16"/>
-    </row>
-    <row r="25" spans="1:6" ht="15">
-      <c r="A25" s="30" t="s">
-        <v>343</v>
-      </c>
-      <c r="B25" s="30" t="s">
-        <v>340</v>
-      </c>
-      <c r="C25" s="30" t="s">
+      <c r="C46" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="E46" s="45"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>402</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>403</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E47" s="45"/>
+    </row>
+    <row r="48" spans="1:5" ht="29.25">
+      <c r="A48" s="25" t="s">
+        <v>405</v>
+      </c>
+      <c r="B48" s="25" t="s">
         <v>341</v>
       </c>
-      <c r="D25" s="30" t="s">
-        <v>344</v>
-      </c>
-      <c r="F25" s="16"/>
-    </row>
-    <row r="26" spans="1:6" ht="15">
-      <c r="A26" s="30" t="s">
-        <v>345</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>346</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D26" s="30" t="s">
-        <v>347</v>
-      </c>
-      <c r="F26" s="16"/>
-    </row>
-    <row r="27" spans="1:6" ht="15">
-      <c r="A27" s="30" t="s">
-        <v>348</v>
-      </c>
-      <c r="B27" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="D27" s="30" t="s">
-        <v>349</v>
-      </c>
-      <c r="F27" s="16"/>
-    </row>
-    <row r="28" spans="1:6" ht="15">
-      <c r="A28" s="30" t="s">
-        <v>350</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>351</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="F28" s="16"/>
-    </row>
-    <row r="29" spans="1:6" ht="29.25">
-      <c r="A29" s="30" t="s">
-        <v>352</v>
-      </c>
-      <c r="B29" s="30" t="s">
-        <v>353</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="30" t="s">
-        <v>354</v>
-      </c>
-      <c r="F29" s="16"/>
-    </row>
-    <row r="30" spans="1:6" ht="15">
-      <c r="A30" s="30" t="s">
-        <v>355</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>356</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>357</v>
-      </c>
-      <c r="F30" s="16"/>
-    </row>
-    <row r="31" spans="1:6" ht="15">
-      <c r="A31" s="30" t="s">
-        <v>358</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>356</v>
-      </c>
-      <c r="C31" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D31" s="30" t="s">
-        <v>359</v>
-      </c>
-      <c r="F31" s="16"/>
-    </row>
-    <row r="32" spans="1:6" ht="29.25">
-      <c r="A32" s="30" t="s">
-        <v>360</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>361</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>362</v>
-      </c>
-      <c r="D32" s="30" t="s">
-        <v>363</v>
-      </c>
-      <c r="F32" s="16"/>
-    </row>
-    <row r="33" spans="1:6" ht="15">
-      <c r="A33" s="30" t="s">
-        <v>364</v>
-      </c>
-      <c r="B33" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="F33" s="16"/>
-    </row>
-    <row r="34" spans="1:6" ht="43.5">
-      <c r="A34" s="30" t="s">
-        <v>366</v>
-      </c>
-      <c r="B34" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="C34" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="D34" s="32" t="s">
-        <v>368</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="15">
-      <c r="A35" s="30" t="s">
-        <v>370</v>
-      </c>
-      <c r="B35" s="30" t="s">
-        <v>371</v>
-      </c>
-      <c r="C35" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="D35" s="32" t="s">
-        <v>372</v>
-      </c>
-      <c r="F35" s="16"/>
-    </row>
-    <row r="36" spans="1:6" ht="15">
-      <c r="A36" s="30" t="s">
-        <v>373</v>
-      </c>
-      <c r="B36" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="C36" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="F36" s="16"/>
-    </row>
-    <row r="37" spans="1:6" ht="29.25">
-      <c r="A37" s="30" t="s">
-        <v>376</v>
-      </c>
-      <c r="B37" s="30" t="s">
-        <v>353</v>
-      </c>
-      <c r="C37" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="30" t="s">
+      <c r="C48" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="E48" s="45"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="25" t="s">
+        <v>406</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>407</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>408</v>
+      </c>
+      <c r="E49" s="45"/>
+    </row>
+    <row r="50" spans="1:8" ht="29.25">
+      <c r="A50" s="25" t="s">
+        <v>409</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>407</v>
+      </c>
+      <c r="C50" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>410</v>
+      </c>
+      <c r="E50" s="45"/>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="B51" s="25" t="s">
         <v>377</v>
       </c>
-      <c r="F37" s="16"/>
-    </row>
-    <row r="38" spans="1:6" ht="15">
-      <c r="A38" s="30" t="s">
-        <v>378</v>
-      </c>
-      <c r="B38" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="C38" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>190</v>
-      </c>
-      <c r="F38" s="16"/>
-    </row>
-    <row r="39" spans="1:6" ht="15">
-      <c r="A39" s="30" t="s">
-        <v>379</v>
-      </c>
-      <c r="B39" s="30" t="s">
-        <v>331</v>
-      </c>
-      <c r="C39" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="D39" s="32" t="s">
-        <v>380</v>
-      </c>
-      <c r="F39" s="16"/>
-    </row>
-    <row r="40" spans="1:6" ht="29.25">
-      <c r="A40" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="B40" s="30" t="s">
-        <v>382</v>
-      </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30" t="s">
-        <v>383</v>
-      </c>
-      <c r="F40" s="16"/>
-    </row>
-    <row r="41" spans="1:6" ht="15">
-      <c r="A41" s="30" t="s">
-        <v>384</v>
-      </c>
-      <c r="B41" s="30" t="s">
-        <v>382</v>
-      </c>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30" t="s">
-        <v>385</v>
-      </c>
-      <c r="F41" s="16"/>
-    </row>
-    <row r="42" spans="1:6" ht="15">
-      <c r="A42" s="30" t="s">
-        <v>386</v>
-      </c>
-      <c r="B42" s="30" t="s">
-        <v>387</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>388</v>
-      </c>
-      <c r="F42" s="16"/>
-    </row>
-    <row r="43" spans="1:6" ht="15">
-      <c r="A43" s="30" t="s">
-        <v>389</v>
-      </c>
-      <c r="B43" s="30" t="s">
-        <v>390</v>
-      </c>
-      <c r="C43" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="D43" s="32" t="s">
-        <v>391</v>
-      </c>
-      <c r="F43" s="16"/>
-    </row>
-    <row r="44" spans="1:6" ht="15">
-      <c r="A44" s="30" t="s">
-        <v>392</v>
-      </c>
-      <c r="B44" s="30" t="s">
-        <v>390</v>
-      </c>
-      <c r="C44" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="D44" s="30" t="s">
-        <v>393</v>
-      </c>
-      <c r="F44" s="16"/>
-    </row>
-    <row r="45" spans="1:6" ht="43.5">
-      <c r="A45" s="30" t="s">
-        <v>394</v>
-      </c>
-      <c r="B45" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="C45" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="30" t="s">
-        <v>395</v>
-      </c>
-      <c r="F45" s="16"/>
-    </row>
-    <row r="46" spans="1:6" ht="29.25">
-      <c r="A46" s="30" t="s">
-        <v>396</v>
-      </c>
-      <c r="B46" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>397</v>
-      </c>
-      <c r="F46" s="16"/>
-    </row>
-    <row r="47" spans="1:6" ht="15">
-      <c r="A47" s="30" t="s">
-        <v>398</v>
-      </c>
-      <c r="B47" s="30" t="s">
-        <v>399</v>
-      </c>
-      <c r="C47" s="30" t="s">
-        <v>400</v>
-      </c>
-      <c r="D47" s="30" t="s">
-        <v>401</v>
-      </c>
-      <c r="F47" s="16"/>
-    </row>
-    <row r="48" spans="1:6" ht="29.25">
-      <c r="A48" s="30" t="s">
-        <v>402</v>
-      </c>
-      <c r="B48" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="C48" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="F48" s="16"/>
-    </row>
-    <row r="49" spans="1:9" ht="15">
-      <c r="A49" s="30" t="s">
-        <v>403</v>
-      </c>
-      <c r="B49" s="30" t="s">
-        <v>404</v>
-      </c>
-      <c r="C49" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="D49" s="30" t="s">
-        <v>405</v>
-      </c>
-      <c r="F49" s="16"/>
-    </row>
-    <row r="50" spans="1:9" ht="29.25">
-      <c r="A50" s="30" t="s">
-        <v>406</v>
-      </c>
-      <c r="B50" s="30" t="s">
-        <v>404</v>
-      </c>
-      <c r="C50" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="D50" s="30" t="s">
-        <v>407</v>
-      </c>
-      <c r="F50" s="16"/>
-    </row>
-    <row r="51" spans="1:9" ht="15">
-      <c r="A51" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="B51" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="C51" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="F51" s="16"/>
-    </row>
-    <row r="52" spans="1:9" ht="15">
-      <c r="A52" s="30" t="s">
-        <v>408</v>
-      </c>
-      <c r="B52" s="30" t="s">
-        <v>409</v>
-      </c>
-      <c r="C52" s="30" t="s">
-        <v>410</v>
-      </c>
-      <c r="D52" s="30" t="s">
+      <c r="C51" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="E51" s="45"/>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="25" t="s">
         <v>411</v>
       </c>
-      <c r="F52" s="16"/>
-    </row>
-    <row r="53" spans="1:9" ht="15">
-      <c r="A53" s="30" t="s">
+      <c r="B52" s="25" t="s">
         <v>412</v>
       </c>
-      <c r="B53" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="C53" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="30" t="s">
+      <c r="C52" s="25" t="s">
         <v>413</v>
       </c>
-      <c r="F53" s="17"/>
+      <c r="D52" s="25" t="s">
+        <v>414</v>
+      </c>
+      <c r="E52" s="45"/>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="25" t="s">
+        <v>415</v>
+      </c>
+      <c r="B53" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="25" t="s">
+        <v>416</v>
+      </c>
+      <c r="E53" s="46"/>
+      <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" spans="1:9" ht="15">
-      <c r="A54" s="30" t="s">
-        <v>414</v>
-      </c>
-      <c r="B54" s="30" t="s">
-        <v>415</v>
-      </c>
-      <c r="C54" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="D54" s="30" t="s">
-        <v>416</v>
-      </c>
-      <c r="F54" s="42" t="s">
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="25" t="s">
         <v>417</v>
       </c>
+      <c r="B54" s="25" t="s">
+        <v>418</v>
+      </c>
+      <c r="C54" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="D54" s="25" t="s">
+        <v>419</v>
+      </c>
+      <c r="E54" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" spans="1:9" ht="15">
-      <c r="A55" s="30" t="s">
-        <v>418</v>
-      </c>
-      <c r="B55" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="C55" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="F55" s="17"/>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="25" t="s">
+        <v>421</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="E55" s="46"/>
+      <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-    </row>
-    <row r="56" spans="1:9" ht="15">
-      <c r="A56" s="30" t="s">
-        <v>419</v>
-      </c>
-      <c r="B56" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="C56" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="F56" s="17"/>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="25" t="s">
+        <v>422</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="E56" s="46"/>
+      <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" spans="1:9" ht="15">
-      <c r="A57" s="30" t="s">
-        <v>420</v>
-      </c>
-      <c r="B57" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="C57" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="30" t="s">
-        <v>421</v>
-      </c>
-      <c r="F57" s="17"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="25" t="s">
+        <v>423</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="25" t="s">
+        <v>424</v>
+      </c>
+      <c r="E57" s="46"/>
+      <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" spans="1:9" ht="29.25">
-      <c r="A58" s="30" t="s">
-        <v>422</v>
-      </c>
-      <c r="B58" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="C58" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D58" s="30" t="s">
-        <v>424</v>
-      </c>
-      <c r="F58" s="17"/>
+    </row>
+    <row r="58" spans="1:8" ht="29.25">
+      <c r="A58" s="25" t="s">
+        <v>425</v>
+      </c>
+      <c r="B58" s="25" t="s">
+        <v>426</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D58" s="25" t="s">
+        <v>427</v>
+      </c>
+      <c r="E58" s="46"/>
+      <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-    </row>
-    <row r="59" spans="1:9" ht="15">
-      <c r="A59" s="30" t="s">
-        <v>425</v>
-      </c>
-      <c r="B59" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="C59" s="30" t="s">
-        <v>295</v>
-      </c>
-      <c r="D59" s="30" t="s">
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="25" t="s">
+        <v>428</v>
+      </c>
+      <c r="B59" s="25" t="s">
         <v>426</v>
       </c>
-      <c r="F59" s="17"/>
+      <c r="C59" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D59" s="25" t="s">
+        <v>429</v>
+      </c>
+      <c r="E59" s="46"/>
+      <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" spans="1:9" ht="15">
-      <c r="A60" s="30" t="s">
-        <v>427</v>
-      </c>
-      <c r="B60" s="30" t="s">
-        <v>428</v>
-      </c>
-      <c r="C60" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="D60" s="30" t="s">
-        <v>429</v>
-      </c>
-      <c r="F60" s="17"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="B60" s="25" t="s">
+        <v>431</v>
+      </c>
+      <c r="C60" s="26" t="s">
+        <v>335</v>
+      </c>
+      <c r="D60" s="25" t="s">
+        <v>432</v>
+      </c>
+      <c r="E60" s="46"/>
+      <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-    </row>
-    <row r="61" spans="1:9" ht="15">
-      <c r="A61" s="30" t="s">
-        <v>430</v>
-      </c>
-      <c r="B61" s="30" t="s">
-        <v>431</v>
-      </c>
-      <c r="C61" s="30" t="s">
-        <v>432</v>
-      </c>
-      <c r="D61" s="30" t="s">
+    </row>
+    <row r="61" spans="1:8" ht="29.25">
+      <c r="A61" s="62" t="s">
         <v>433</v>
       </c>
-      <c r="F61" s="17"/>
+      <c r="B61" s="62" t="s">
+        <v>434</v>
+      </c>
+      <c r="C61" s="62" t="s">
+        <v>435</v>
+      </c>
+      <c r="D61" s="62" t="s">
+        <v>436</v>
+      </c>
+      <c r="E61" s="63" t="s">
+        <v>437</v>
+      </c>
+      <c r="F61" s="1"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" spans="1:9" ht="15"/>
-    <row r="63" spans="1:9" ht="15"/>
-    <row r="64" spans="1:9" ht="15"/>
-    <row r="65" ht="15"/>
-    <row r="66" ht="15"/>
-    <row r="67" ht="15"/>
+    </row>
+    <row r="62" spans="1:8" ht="29.25">
+      <c r="A62" s="29" t="s">
+        <v>438</v>
+      </c>
+      <c r="B62" s="29" t="s">
+        <v>439</v>
+      </c>
+      <c r="C62" s="29" t="s">
+        <v>403</v>
+      </c>
+      <c r="D62" s="29"/>
+      <c r="E62" s="63" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8"/>
+    <row r="64" spans="1:8"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
   </sheetData>
-  <autoFilter ref="A1:E61" xr:uid="{57DB3D55-2C7D-4E44-BB5E-763AFC2F400D}"/>
+  <autoFilter ref="A1:D61" xr:uid="{57DB3D55-2C7D-4E44-BB5E-763AFC2F400D}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4845,136 +5010,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="34" t="s">
-        <v>434</v>
-      </c>
-      <c r="B1" s="34" t="s">
-        <v>435</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>273</v>
+      <c r="A1" s="28" t="s">
+        <v>440</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>441</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="35" t="s">
-        <v>436</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>437</v>
-      </c>
-      <c r="C2" s="35"/>
+      <c r="A2" s="29" t="s">
+        <v>442</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>443</v>
+      </c>
+      <c r="C2" s="29"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="35" t="s">
-        <v>438</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>439</v>
-      </c>
-      <c r="C3" s="35"/>
+      <c r="A3" s="29" t="s">
+        <v>444</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>445</v>
+      </c>
+      <c r="C3" s="29"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="35" t="s">
-        <v>440</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>441</v>
-      </c>
-      <c r="C4" s="35"/>
+      <c r="A4" s="29" t="s">
+        <v>446</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>447</v>
+      </c>
+      <c r="C4" s="29"/>
     </row>
     <row r="5" spans="1:3" ht="57.95">
-      <c r="A5" s="35" t="s">
-        <v>442</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>443</v>
-      </c>
-      <c r="C5" s="35"/>
+      <c r="A5" s="29" t="s">
+        <v>448</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>449</v>
+      </c>
+      <c r="C5" s="29"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="35" t="s">
-        <v>444</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>444</v>
-      </c>
-      <c r="C6" s="35"/>
+      <c r="A6" s="29" t="s">
+        <v>450</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>450</v>
+      </c>
+      <c r="C6" s="29"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="35" t="s">
-        <v>445</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>446</v>
-      </c>
-      <c r="C7" s="35"/>
+      <c r="A7" s="29" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>452</v>
+      </c>
+      <c r="C7" s="29"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>328</v>
-      </c>
-      <c r="C8" s="35"/>
+      <c r="A8" s="29" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="C8" s="29"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="35" t="s">
-        <v>448</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>449</v>
-      </c>
-      <c r="C9" s="35"/>
+      <c r="A9" s="29" t="s">
+        <v>454</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>455</v>
+      </c>
+      <c r="C9" s="29"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="35" t="s">
-        <v>450</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>451</v>
-      </c>
-      <c r="C10" s="35"/>
+      <c r="A10" s="29" t="s">
+        <v>456</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>457</v>
+      </c>
+      <c r="C10" s="29"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="35" t="s">
-        <v>452</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>453</v>
-      </c>
-      <c r="C11" s="35"/>
+      <c r="A11" s="29" t="s">
+        <v>458</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>459</v>
+      </c>
+      <c r="C11" s="29"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="35" t="s">
-        <v>454</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>328</v>
-      </c>
-      <c r="C12" s="35"/>
+      <c r="A12" s="29" t="s">
+        <v>460</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="C12" s="29"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="35" t="s">
-        <v>455</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>456</v>
-      </c>
-      <c r="C13" s="35"/>
+      <c r="A13" s="29" t="s">
+        <v>461</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="C13" s="29"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="35" t="s">
-        <v>457</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>328</v>
-      </c>
-      <c r="C14" s="35"/>
+      <c r="A14" s="29" t="s">
+        <v>463</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="C14" s="29"/>
     </row>
     <row r="17" spans="1:1" ht="15">
-      <c r="A17" s="29" t="s">
-        <v>458</v>
+      <c r="A17" s="24" t="s">
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -4983,6 +5148,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="de233cd9-83bc-44d2-9183-9acc155145f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="84f23406-1ae4-465c-a962-53264b1fc517" xsi:nil="true"/>
+    <MediaLengthInSeconds xmlns="de233cd9-83bc-44d2-9183-9acc155145f0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4991,7 +5168,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B4CDCE25E282314583853F0A9C0F4B99" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="83495db65c20406778c5cb079511534a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="de233cd9-83bc-44d2-9183-9acc155145f0" xmlns:ns3="84f23406-1ae4-465c-a962-53264b1fc517" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ed81be00ee71557f52259e8353b6b866" ns2:_="" ns3:_="">
     <xsd:import namespace="de233cd9-83bc-44d2-9183-9acc155145f0"/>
@@ -5186,25 +5363,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="de233cd9-83bc-44d2-9183-9acc155145f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="84f23406-1ae4-465c-a962-53264b1fc517" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39CC3E43-3C84-4BD7-B314-4239EDA621C1}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66C5DCD2-D241-4773-831A-D8D79E5BA0B9}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B99E8C79-E827-4520-8D8B-A9804826F8CD}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39CC3E43-3C84-4BD7-B314-4239EDA621C1}"/>
 </file>